--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92562833463</v>
+        <v>46157.93073927313</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93073927313</v>
+        <v>46157.93156156102</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93156156102</v>
+        <v>46157.93394501202</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93394501202</v>
+        <v>46157.9371016999</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9371016999</v>
+        <v>46158.28211434358</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28211434358</v>
+        <v>46158.29667313403</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29667313403</v>
+        <v>46158.29806836665</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29806836665</v>
+        <v>46158.33382260185</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33382260185</v>
+        <v>46158.36849481524</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36849481524</v>
+        <v>46158.37282387156</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
